--- a/resources/library/xlsx/marketing-budget.xlsx
+++ b/resources/library/xlsx/marketing-budget.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" r:id="Rb080dc56e6e542f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Re7a9aee6df0242d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R138d0e239e2c46c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" r:id="Rec67f77142774879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R6ebdafe444b0440b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R12c6d3c27b7e4860"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -170,6 +170,102 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="22230232-6093-4262-ab7b-24a46d9a1862"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rcfbaeb62775d41c1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="ab918252-13ba-4caf-8526-109a6af35ea0"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R62e446a4ed1643af"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="81a9276b-6ae2-4925-9953-deb96e4623b4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb9f7f34104414bd1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -380,7 +476,7 @@
     <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -1559,6 +1655,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dff97601c714b46"/>
 </x:worksheet>
 </file>
 
@@ -1573,7 +1670,7 @@
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -2634,6 +2731,7 @@
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd869e9f484bf4aad"/>
 </x:worksheet>
 </file>
 
@@ -2648,7 +2746,7 @@
     <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -3714,5 +3812,6 @@
     <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a6487693c4f455a"/>
 </x:worksheet>
 </file>